--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.63047641712476</v>
+        <v>2.377452417782774</v>
       </c>
       <c r="D2" t="n">
-        <v>11.72002722982732</v>
+        <v>1.904504424846939</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7950206311985</v>
+        <v>1.754190852569756</v>
       </c>
       <c r="F2" t="n">
-        <v>14.37420093985428</v>
+        <v>2.335807652726321</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.09286771505349</v>
+        <v>5.702591003696193</v>
       </c>
       <c r="D3" t="n">
-        <v>15.09507639015442</v>
+        <v>2.452949913400093</v>
       </c>
       <c r="E3" t="n">
-        <v>10.7950206311985</v>
+        <v>1.754190852569756</v>
       </c>
       <c r="F3" t="n">
-        <v>14.37420093985428</v>
+        <v>2.335807652726321</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.91291827352587</v>
+        <v>7.785849219447954</v>
       </c>
       <c r="D4" t="n">
-        <v>37.11154756822807</v>
+        <v>6.030626479837061</v>
       </c>
       <c r="E4" t="n">
-        <v>10.7950206311985</v>
+        <v>1.754190852569756</v>
       </c>
       <c r="F4" t="n">
-        <v>14.37420093985428</v>
+        <v>2.335807652726321</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.86201406823648</v>
+        <v>8.427577286088429</v>
       </c>
       <c r="D5" t="n">
-        <v>48.65042455884328</v>
+        <v>7.905693990812033</v>
       </c>
       <c r="E5" t="n">
-        <v>10.7950206311985</v>
+        <v>1.754190852569756</v>
       </c>
       <c r="F5" t="n">
-        <v>14.37420093985428</v>
+        <v>2.335807652726321</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.93136538082408</v>
+        <v>5.188846874383913</v>
       </c>
       <c r="D6" t="n">
-        <v>30.68281061758589</v>
+        <v>4.985956725357707</v>
       </c>
       <c r="E6" t="n">
-        <v>10.7950206311985</v>
+        <v>1.754190852569756</v>
       </c>
       <c r="F6" t="n">
-        <v>14.37420093985428</v>
+        <v>2.335807652726321</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.94225592930257</v>
+        <v>4.703116588511668</v>
       </c>
       <c r="D7" t="n">
-        <v>21.22470973934856</v>
+        <v>3.449015332644141</v>
       </c>
       <c r="E7" t="n">
-        <v>10.7950206311985</v>
+        <v>1.754190852569756</v>
       </c>
       <c r="F7" t="n">
-        <v>14.37420093985428</v>
+        <v>2.335807652726321</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.23883535530367</v>
+        <v>3.451310745236847</v>
       </c>
       <c r="D8" t="n">
-        <v>30.87228270577375</v>
+        <v>5.016745939688234</v>
       </c>
       <c r="E8" t="n">
-        <v>10.7950206311985</v>
+        <v>1.754190852569756</v>
       </c>
       <c r="F8" t="n">
-        <v>14.37420093985428</v>
+        <v>2.335807652726321</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.30529159727389</v>
+        <v>3.299609884557008</v>
       </c>
       <c r="D9" t="n">
-        <v>38.62852817202555</v>
+        <v>6.277135827954153</v>
       </c>
       <c r="E9" t="n">
-        <v>10.7950206311985</v>
+        <v>1.754190852569756</v>
       </c>
       <c r="F9" t="n">
-        <v>14.37420093985428</v>
+        <v>2.335807652726321</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.19646792993373</v>
+        <v>4.581926038614231</v>
       </c>
       <c r="D10" t="n">
-        <v>37.80463753585457</v>
+        <v>6.143253599576369</v>
       </c>
       <c r="E10" t="n">
-        <v>10.7950206311985</v>
+        <v>1.754190852569756</v>
       </c>
       <c r="F10" t="n">
-        <v>14.37420093985428</v>
+        <v>2.335807652726321</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.15392178620302</v>
+        <v>4.900012290257992</v>
       </c>
       <c r="D11" t="n">
-        <v>43.25763852792913</v>
+        <v>7.029366260788484</v>
       </c>
       <c r="E11" t="n">
-        <v>10.7950206311985</v>
+        <v>1.754190852569756</v>
       </c>
       <c r="F11" t="n">
-        <v>14.37420093985428</v>
+        <v>2.335807652726321</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.42393810389467</v>
+        <v>3.806389941882885</v>
       </c>
       <c r="D12" t="n">
-        <v>63.85417487848812</v>
+        <v>10.37630341775432</v>
       </c>
       <c r="E12" t="n">
-        <v>10.7950206311985</v>
+        <v>1.754190852569756</v>
       </c>
       <c r="F12" t="n">
-        <v>14.37420093985428</v>
+        <v>2.335807652726321</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
